--- a/Calendario Informe Semanal.xlsx
+++ b/Calendario Informe Semanal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\01 Control de Gestión\01 Reporting\09 Informe Semanal\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAD476E-BF26-4B4A-B8D9-0E99BC85CC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C709DB4D-A4E8-48FF-A39B-7E86CE31A192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="495" firstSheet="1" activeTab="1" xr2:uid="{34D7CF42-36AA-4C05-8F32-0720A30494C1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="495" firstSheet="1" activeTab="1" xr2:uid="{34D7CF42-36AA-4C05-8F32-0720A30494C1}"/>
   </bookViews>
   <sheets>
     <sheet name="calendario 2021" sheetId="1" state="hidden" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="92">
   <si>
     <t>L</t>
   </si>
@@ -283,9 +283,6 @@
   </si>
   <si>
     <t>Sábado 15 de agosto: Asunción de la Virgen</t>
-  </si>
-  <si>
-    <t>Jueves 20 de agosto: Natalicio de Bernardo O´Higgins (Chillán y Chillán Viejo)</t>
   </si>
   <si>
     <t>Viernes 18 de septiembre: Independencia 
@@ -2553,7 +2550,7 @@
       </c>
       <c r="R1" s="28">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
@@ -4678,7 +4675,7 @@
       </c>
       <c r="R53" s="28">
         <f ca="1">R1</f>
-        <v>46098</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="15.5" x14ac:dyDescent="0.35">
@@ -6845,6 +6842,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="H36:N36"/>
     <mergeCell ref="H97:N97"/>
     <mergeCell ref="H45:N45"/>
     <mergeCell ref="H56:N56"/>
@@ -6852,11 +6854,6 @@
     <mergeCell ref="H73:N73"/>
     <mergeCell ref="H81:N81"/>
     <mergeCell ref="H89:N89"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="H36:N36"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -6930,7 +6927,7 @@
       </c>
       <c r="T1" s="28">
         <f ca="1">TODAY()</f>
-        <v>46098</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -7024,7 +7021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="38.65" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="38.65" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B6" s="42"/>
       <c r="I6" s="43"/>
       <c r="J6" s="43"/>
@@ -7050,10 +7047,10 @@
       <c r="R6" s="41"/>
       <c r="S6" s="21"/>
       <c r="T6" s="32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="39.75" customHeight="1" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <f>+MONTH(K6)</f>
         <v>12</v>
@@ -8189,7 +8186,7 @@
         <v>Informe 6 días ( 5 reales y 1 proyectado); Reales del 27/3 al 31/4 ,Proyectado 1/4)</v>
       </c>
       <c r="T31" s="32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8706,12 +8703,12 @@
         <v>5</v>
       </c>
       <c r="D42" s="14">
-        <f>+DAY(L42)</f>
-        <v>21</v>
+        <f>+DAY(J42)</f>
+        <v>19</v>
       </c>
       <c r="E42" s="15">
         <f t="shared" si="31"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" s="14">
         <f t="shared" si="32"/>
@@ -8725,7 +8722,7 @@
         <f t="shared" si="29"/>
         <v>46161</v>
       </c>
-      <c r="K42" s="8">
+      <c r="K42" s="9">
         <f t="shared" si="29"/>
         <v>46162</v>
       </c>
@@ -8733,7 +8730,7 @@
         <f t="shared" si="29"/>
         <v>46163</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="7">
         <f t="shared" si="29"/>
         <v>46164</v>
       </c>
@@ -8747,18 +8744,18 @@
       </c>
       <c r="Q42" s="39">
         <f>DATE($A$1,C42,D42+1)</f>
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="R42" s="41">
         <f t="shared" si="34"/>
         <v>20</v>
       </c>
       <c r="S42" s="21" t="str">
-        <f>IF(A42=C42,"Informe "&amp;D42-B42+1&amp;" días ( "&amp;D42-B42&amp;" reales y 1 proyectado); Reales del "&amp;B42&amp;"/"&amp;C42&amp;" al "&amp;D42-1&amp;"/"&amp;A42&amp;" ,Proyectado "&amp;D42&amp;"/"&amp;A42,"Informe "&amp;DAY(EOMONTH(L42,0))-B42+D42+1&amp;" días ( "&amp;DAY(EOMONTH(L42,0))-B42+D42&amp;" reales y 1 proyectado); Reales del "&amp;B42&amp;"/"&amp;A42&amp;" al "&amp;D42-1&amp;"/"&amp;C42&amp;" ,Proyectado "&amp;D42&amp;"/"&amp;C42)</f>
-        <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 15/5 al 20/5 ,Proyectado 21/5</v>
+        <f>IF(A42=C42,"Informe "&amp;D42-B42+1&amp;" días ( "&amp;D42-B42&amp;" reales y 1 proyectado); Reales del "&amp;B42&amp;"/"&amp;C42&amp;" al "&amp;D42-1&amp;"/"&amp;A42&amp;" ,Proyectado "&amp;D42&amp;"/"&amp;A42,"Informe "&amp;DAY(EOMONTH(J42,0))-B42+D42+1&amp;" días ( "&amp;DAY(EOMONTH(J42,0))-B42+D42&amp;" reales y 1 proyectado); Reales del "&amp;B42&amp;"/"&amp;A42&amp;" al "&amp;D42-1&amp;"/"&amp;C42&amp;" ,Proyectado "&amp;D42&amp;"/"&amp;C42)</f>
+        <v>Informe 5 días ( 4 reales y 1 proyectado); Reales del 15/5 al 18/5 ,Proyectado 19/5</v>
       </c>
       <c r="T42" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8767,8 +8764,8 @@
         <v>5</v>
       </c>
       <c r="B43" s="14">
-        <f>+DAY(M42)</f>
-        <v>22</v>
+        <f>+DAY(K42)</f>
+        <v>20</v>
       </c>
       <c r="C43" s="14">
         <f>+MONTH(L43)</f>
@@ -8780,7 +8777,7 @@
       </c>
       <c r="E43" s="15">
         <f>IF(A43=C43,D43-B43+1,DAY(EOMONTH(J43,0))-B43+D43+1)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43" s="14">
         <f>+F42+1</f>
@@ -8824,7 +8821,7 @@
       </c>
       <c r="S43" s="21" t="str">
         <f>IF(A43=C43,"Informe "&amp;D43-B43+1&amp;" días ( "&amp;D43-B43&amp;" reales y 1 proyectado); Reales del "&amp;B43&amp;"/"&amp;C43&amp;" al "&amp;D43-1&amp;"/"&amp;A43&amp;" ,Proyectado "&amp;D43&amp;"/"&amp;A43,"Informe "&amp;DAY(EOMONTH(L43,0))-B43+D43+1&amp;" días ( "&amp;DAY(EOMONTH(L43,0))-B43+D43&amp;" reales y 1 proyectado); Reales del "&amp;B43&amp;"/"&amp;A43&amp;" al "&amp;D43-1&amp;"/"&amp;C43&amp;" ,Proyectado "&amp;D43&amp;"/"&amp;C43)</f>
-        <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 22/5 al 27/5 ,Proyectado 28/5</v>
+        <v>Informe 9 días ( 8 reales y 1 proyectado); Reales del 20/5 al 27/5 ,Proyectado 28/5</v>
       </c>
       <c r="T43" s="32"/>
     </row>
@@ -8963,7 +8960,7 @@
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 29/5 al 3/6 ,Proyectado 4/6</v>
       </c>
       <c r="T47" s="32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -9170,10 +9167,6 @@
       <c r="T50" s="32"/>
     </row>
     <row r="51" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E51" s="15">
-        <f t="shared" si="47"/>
-        <v>1</v>
-      </c>
       <c r="F51" s="14">
         <f>+F50+1</f>
         <v>26</v>
@@ -9204,7 +9197,7 @@
       </c>
       <c r="T52" s="28">
         <f ca="1">T1</f>
-        <v>46098</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.5" x14ac:dyDescent="0.35">
@@ -9355,8 +9348,8 @@
         <v>26</v>
       </c>
       <c r="S57" s="21" t="str">
-        <f>IF(A57=C57,"Informe "&amp;D57-B57+1&amp;" días ( "&amp;D57-B57&amp;" reales y 1 proyectado); Reales del "&amp;B57&amp;"/"&amp;C57&amp;" al "&amp;D57-1&amp;"/"&amp;A57&amp;" ,Proyectado "&amp;D57&amp;"/"&amp;A57,"Informe "&amp;DAY(EOMONTH(M51,0))-B57+D57+1&amp;" días ( "&amp;DAY(EOMONTH(M51,0))-B57+D57&amp;" reales y 1 proyectado); Reales del "&amp;B57&amp;"/"&amp;A57&amp;" al "&amp;D57-1&amp;"/"&amp;C57&amp;" ,Proyectado "&amp;D57&amp;"/"&amp;C57)</f>
-        <v>Informe 8 días ( 7 reales y 1 proyectado); Reales del 26/6 al 1/7 ,Proyectado 2/7</v>
+        <f>IF(A57=C57,"Informe "&amp;D57-B57+1&amp;" días ( "&amp;D57-B57&amp;" reales y 1 proyectado); Reales del "&amp;B57&amp;"/"&amp;C57&amp;" al "&amp;D57-1&amp;"/"&amp;A57&amp;" ,Proyectado "&amp;D57&amp;"/"&amp;A57,"Informe "&amp;DAY(EOMONTH(M51,0))-B57+D57&amp;" días ( "&amp;DAY(EOMONTH(M51,0))-B57+D57-1&amp;" reales y 1 proyectado); Reales del "&amp;B57&amp;"/"&amp;A57&amp;" al "&amp;D57-1&amp;"/"&amp;C57&amp;" ,Proyectado "&amp;D57&amp;"/"&amp;C57)</f>
+        <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 26/6 al 1/7 ,Proyectado 2/7</v>
       </c>
       <c r="T57" s="32"/>
     </row>
@@ -9441,12 +9434,12 @@
         <v>7</v>
       </c>
       <c r="D59" s="14">
-        <f>+DAY(L59)</f>
-        <v>16</v>
+        <f>+DAY(J59)</f>
+        <v>14</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="50"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F59" s="14">
         <f t="shared" ref="F59:F61" si="54">1+F58</f>
@@ -9460,7 +9453,7 @@
         <f t="shared" si="52"/>
         <v>46217</v>
       </c>
-      <c r="K59" s="8">
+      <c r="K59" s="9">
         <f t="shared" si="52"/>
         <v>46218</v>
       </c>
@@ -9468,7 +9461,7 @@
         <f t="shared" si="52"/>
         <v>46219</v>
       </c>
-      <c r="M59" s="9">
+      <c r="M59" s="7">
         <f t="shared" si="52"/>
         <v>46220</v>
       </c>
@@ -9482,7 +9475,7 @@
       </c>
       <c r="Q59" s="39">
         <f t="shared" si="53"/>
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="R59" s="41">
         <f>R58+1</f>
@@ -9490,10 +9483,10 @@
       </c>
       <c r="S59" s="21" t="str">
         <f>IF(A59=C59,"Informe "&amp;D59-B59+1&amp;" días ( "&amp;D59-B59&amp;" reales y 1 proyectado); Reales del "&amp;B59&amp;"/"&amp;C59&amp;" al "&amp;D59-1&amp;"/"&amp;A59&amp;" ,Proyectado "&amp;D59&amp;"/"&amp;A59,"Informe "&amp;DAY(EOMONTH(M51,0))-B59+D59+1&amp;" días ( "&amp;DAY(EOMONTH(M51,0))-B59+D59&amp;" reales y 1 proyectado); Reales del "&amp;B59&amp;"/"&amp;A59&amp;" al "&amp;D59-1&amp;"/"&amp;C59&amp;" ,Proyectado "&amp;D59&amp;"/"&amp;C59)</f>
-        <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 10/7 al 15/7 ,Proyectado 16/7</v>
+        <v>Informe 5 días ( 4 reales y 1 proyectado); Reales del 10/7 al 13/7 ,Proyectado 14/7</v>
       </c>
       <c r="T59" s="32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -9502,8 +9495,8 @@
         <v>7</v>
       </c>
       <c r="B60" s="14">
-        <f>+DAY(M59)</f>
-        <v>17</v>
+        <f>+DAY(K59)</f>
+        <v>15</v>
       </c>
       <c r="C60" s="14">
         <f>+MONTH(L60)</f>
@@ -9515,7 +9508,7 @@
       </c>
       <c r="E60" s="15">
         <f t="shared" si="50"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60" s="14">
         <f t="shared" si="54"/>
@@ -9559,7 +9552,7 @@
       </c>
       <c r="S60" s="21" t="str">
         <f>IF(A60=C60,"Informe "&amp;D60-B60+1&amp;" días ( "&amp;D60-B60&amp;" reales y 1 proyectado); Reales del "&amp;B60&amp;"/"&amp;C60&amp;" al "&amp;D60-1&amp;"/"&amp;A60&amp;" ,Proyectado "&amp;D60&amp;"/"&amp;A60,"Informe "&amp;DAY(EOMONTH(M60,0))-B60+D60+1&amp;" días ( "&amp;DAY(EOMONTH(M60,0))-B60+D60&amp;" reales y 1 proyectado); Reales del "&amp;B60&amp;"/"&amp;A60&amp;" al "&amp;D60-1&amp;"/"&amp;C60&amp;" ,Proyectado "&amp;D60&amp;"/"&amp;C60)</f>
-        <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 17/7 al 22/7 ,Proyectado 23/7</v>
+        <v>Informe 9 días ( 8 reales y 1 proyectado); Reales del 15/7 al 22/7 ,Proyectado 23/7</v>
       </c>
       <c r="T60" s="32"/>
     </row>
@@ -9890,7 +9883,7 @@
         <f t="shared" si="59"/>
         <v>46253</v>
       </c>
-      <c r="L68" s="7">
+      <c r="L68" s="9">
         <f t="shared" si="59"/>
         <v>46254</v>
       </c>
@@ -9918,9 +9911,7 @@
         <f>IF(A68=C68,"Informe "&amp;D68-B68+1&amp;" días ( "&amp;D68-B68&amp;" reales y 1 proyectado); Reales del "&amp;B68&amp;"/"&amp;C68&amp;" al "&amp;D68-1&amp;"/"&amp;A68&amp;" ,Proyectado "&amp;D68&amp;"/"&amp;A68,"Informe "&amp;DAY(EOMONTH(L67,0))-B68+D68+1&amp;" días ( "&amp;DAY(EOMONTH(L67,0))-B68+D68&amp;" reales y 1 proyectado); Reales del "&amp;B68&amp;"/"&amp;A68&amp;" al "&amp;D68-1&amp;"/"&amp;C68&amp;" ,Proyectado "&amp;D68&amp;"/"&amp;C68)</f>
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 14/8 al 19/8 ,Proyectado 20/8</v>
       </c>
-      <c r="T68" s="32" t="s">
-        <v>80</v>
-      </c>
+      <c r="T68" s="32"/>
     </row>
     <row r="69" spans="1:20" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="14">
@@ -10277,7 +10268,7 @@
         <v>Informe 6 días ( 5 reales y 1 proyectado); Reales del 11/9 al 15/9 ,Proyectado 16/9</v>
       </c>
       <c r="T75" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -10630,7 +10621,7 @@
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 9/10 al 14/10 ,Proyectado 15/10</v>
       </c>
       <c r="T83" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -10763,7 +10754,7 @@
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 23/10 al 28/10 ,Proyectado 29/10</v>
       </c>
       <c r="T85" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.35">
@@ -10855,7 +10846,7 @@
       <c r="R89" s="41"/>
       <c r="S89" s="21"/>
       <c r="T89" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:20" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -11306,7 +11297,7 @@
         <f t="shared" ref="F98:F100" si="95">1+F97</f>
         <v>#REF!</v>
       </c>
-      <c r="I98" s="9">
+      <c r="I98" s="7">
         <f>1+O97</f>
         <v>46363</v>
       </c>
@@ -11347,7 +11338,7 @@
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 4/12 al 9/12 ,Proyectado 10/12</v>
       </c>
       <c r="T98" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -11483,7 +11474,7 @@
         <v>Informe 6 días ( 5 reales y 1 proyectado); Reales del 18/12 al 22/12 ,Proyectado 23/12</v>
       </c>
       <c r="T100" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="38.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -11538,7 +11529,7 @@
         <v>Informe 7 días ( 6 reales y 1 proyectado); Reales del 24/12 al 29/12 ,Proyectado 30/12</v>
       </c>
       <c r="T101" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.35">
@@ -12569,15 +12560,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CAB26C5234A12E419316CB59C6D7D393" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b53fa7be3030560a3debdd7abaf626d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf8265-5d49-4303-8d6c-a3e3dc13898a" xmlns:ns3="70b3a8a4-10f1-4453-b557-059c8aa2e01d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f9a576095bf226b167e08e8482324ea" ns2:_="" ns3:_="">
     <xsd:import namespace="36cf8265-5d49-4303-8d6c-a3e3dc13898a"/>
@@ -12832,6 +12814,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BED16C8-9A0B-4F8D-8C87-DB79587E909F}">
   <ds:schemaRefs>
@@ -12844,14 +12835,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092B6C16-CB85-42B4-926C-8DE289F773F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{096EFB29-91B5-4759-A3C4-1334E445E247}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12868,4 +12851,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092B6C16-CB85-42B4-926C-8DE289F773F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>